--- a/output/laminas_comunales/comunal_m_saldomigr_a_2022_biobio.xlsx
+++ b/output/laminas_comunales/comunal_m_saldomigr_a_2022_biobio.xlsx
@@ -1095,7 +1095,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2018_2022. Escala de colores estandarizada a nivel nacional para todo el periodo.</t>
+          <t>Periodo 2018_2022. Escala comunal recortada a percentiles 3-97. Sobre umbral: Los Angeles (5.171); Concepción (7.716); San Pedro de la Paz (5.152). Bajo umbral: Hualpén (-7.637).</t>
         </is>
       </c>
     </row>
